--- a/수행평가_구글시트_데모데이터.xlsx
+++ b/수행평가_구글시트_데모데이터.xlsx
@@ -196,6 +196,7 @@
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -219,6 +220,11 @@
           <t>그룹</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -234,6 +240,11 @@
       <c r="C2">
         <v>20</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -254,6 +265,11 @@
           <t>의복 디자인하기</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -274,6 +290,11 @@
           <t>의복 디자인하기</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>이번 수행</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -289,6 +310,11 @@
       <c r="C5">
         <v>20</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -309,6 +335,11 @@
           <t>기술적 문제 해결 및 발명품 기획 프로젝트</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -329,8 +360,18 @@
           <t>기술적 문제 해결 및 발명품 기획 프로젝트</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="영역 상태" error="완료, 이번 수행, 예정 중에서 골라주세요." sqref="E2:E1000">
+      <formula1>"완료,이번 수행,예정"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 
@@ -1165,8 +1206,7 @@
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1192,288 +1232,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>청소년의 건강한 식생활 제안하기</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>나에게 어울리는 옷 디자인하기</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>에코 수세미 제작하기</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>이번 수행</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>청소년의 건강한 식생활 제안하기</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>나에게 어울리는 옷 디자인하기</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>에코 수세미 제작하기</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>이번 수행</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>청소년의 건강한 식생활 제안하기</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>나에게 어울리는 옷 디자인하기</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>에코 수세미 제작하기</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>이번 수행</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>청소년의 건강한 식생활 제안하기</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>나에게 어울리는 옷 디자인하기</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>demo-subject-1</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>에코 수세미 제작하기</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>이번 수행</t>
         </is>
       </c>
     </row>

--- a/수행평가_구글시트_데모데이터.xlsx
+++ b/수행평가_구글시트_데모데이터.xlsx
@@ -7,7 +7,7 @@
     <sheet name="영역" sheetId="3" r:id="rId3"/>
     <sheet name="명단" sheetId="4" r:id="rId4"/>
     <sheet name="점수_기술·가정" sheetId="5" r:id="rId5"/>
-    <sheet name="진행상태" sheetId="6" r:id="rId6"/>
+    <sheet name="영역메모" sheetId="6" r:id="rId6"/>
     <sheet name="결시명단_기술·가정" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>

--- a/수행평가_구글시트_데모데이터.xlsx
+++ b/수행평가_구글시트_데모데이터.xlsx
@@ -7,8 +7,10 @@
     <sheet name="영역" sheetId="3" r:id="rId3"/>
     <sheet name="명단" sheetId="4" r:id="rId4"/>
     <sheet name="점수_기술·가정" sheetId="5" r:id="rId5"/>
+    <sheet name="점수_정보" sheetId="8" r:id="rId9"/>
     <sheet name="영역메모" sheetId="6" r:id="rId6"/>
     <sheet name="결시명단_기술·가정" sheetId="7" r:id="rId7"/>
+    <sheet name="결시명단_정보" sheetId="9" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -185,6 +187,26 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1-1;1-2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>demo-subject-2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -361,6 +383,116 @@
         </is>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>demo-subject-2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>정보 윤리 캠페인 포스터 만들기</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>demo-subject-2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>알고리즘 순서도 그리기</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>20</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>이번 수행</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>demo-subject-2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>조건문 프로그램 만들기</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>25</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>파이썬 프로그래밍 프로젝트</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>demo-subject-2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>반복문 프로그램 만들기</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>25</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>파이썬 프로그래밍 프로젝트</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>demo-subject-2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>데이터 시각화 보고서 쓰기</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -1279,4 +1411,338 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="4" width="6" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="10" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>과목명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>학년</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>반</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>정보 윤리 캠페인 포스터 만들기</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>알고리즘 순서도 그리기</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>조건문 프로그램 만들기</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>반복문 프로그램 만들기</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>데이터 시각화 보고서 쓰기</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>14</v>
+      </c>
+      <c r="G2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>김민준</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>이서연</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>15</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>결시</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>박도윤</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>최지우</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>14</v>
+      </c>
+      <c r="G6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>정하은</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>강서준</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>윤지호</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="4" width="6" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>영역</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>학년</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>반</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>알고리즘 순서도 그리기</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>이서연</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/수행평가_구글시트_데모데이터.xlsx
+++ b/수행평가_구글시트_데모데이터.xlsx
@@ -143,6 +143,7 @@
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -164,6 +165,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>개별수강생</t>
         </is>
       </c>
     </row>

--- a/수행평가_구글시트_데모데이터.xlsx
+++ b/수행평가_구글시트_데모데이터.xlsx
@@ -143,7 +143,6 @@
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -165,11 +164,6 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>개별수강생</t>
         </is>
       </c>
     </row>
